--- a/data/trans_bre/IP16A07-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A07-Estudios-trans_bre.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,14</t>
+          <t>0,0; 11,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,78</t>
+          <t>0,0; 3,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,19</t>
+          <t>0,0; 10,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,48</t>
+          <t>0,31; 3,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A07-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A07-Estudios-trans_bre.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,9</t>
+          <t>0,0; 16,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,08</t>
+          <t>0,0; 3,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,84</t>
+          <t>0,0; 12,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,76</t>
+          <t>0,28; 3,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A07-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A07-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero pastillas para dormir</t>
+          <t>Menores que consumieron pastillas para dormir</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,12</t>
+          <t>0,0; 16,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,6</t>
+          <t>0,0; 3,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>3,47</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,39</t>
+          <t>0,0; 11,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,24</t>
+          <t>0,37; 4,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">

--- a/data/trans_bre/IP16A07-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A07-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,135 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,9</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.7137704734865304</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 16,14</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>4.250520011109771</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,71</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,03</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.1514105803265523</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,47</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,83</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="n">
+        <v>0.7711637599736804</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,44 +755,24 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,45</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,44</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.9384002461333107</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -955,52 +780,116 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,21</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,37; 4,28</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="n">
+        <v>3.446045566783775</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.09225814619632186</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.3284414212451732</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="n">
+        <v>0.0859357388035233</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="n">
+        <v>0.4656875549595054</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="n">
+        <v>0.9252916291024936</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +897,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
